--- a/templates_excel/04_Đánh giá hệ thống hiện tại.xlsx
+++ b/templates_excel/04_Đánh giá hệ thống hiện tại.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/Application_For_Task/templates_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{E7230F2F-CFFB-45BF-80EB-743E8BFDA54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22611804-AF0D-4DAF-A8DF-F93E822EE9D0}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{E7230F2F-CFFB-45BF-80EB-743E8BFDA54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23E84EC-1B75-4031-B7F0-E17A98DF7DE8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng quan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="462">
   <si>
     <t>Mục đích:</t>
   </si>
@@ -1341,7 +1341,94 @@
     <t>sudo iptables -L INPUT -n | grep "10.31.100.18"</t>
   </si>
   <si>
-    <t xml:space="preserve"> Hostname:</t>
+    <t>grep PermitEmptyPasswords /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep UsePAM /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep GSSAPIAuthentication /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep HostbasedAuthentication /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep LogLevel /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep MaxStartups /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>grep ClientAliveInterval /etc/ssh/sshd_config</t>
+  </si>
+  <si>
+    <t>VERBOSE</t>
+  </si>
+  <si>
+    <t>grep -E 'difok|maxrepeat|maxsequence|dictcheck' /etc/security/pwquality.conf</t>
+  </si>
+  <si>
+    <t>grep -E 'deny|unlock_time' /etc/security/faillock.conf</t>
+  </si>
+  <si>
+    <t>grep 'even_deny_root' /etc/security/faillock.conf</t>
+  </si>
+  <si>
+    <t>difok=2, maxrepeat=3, maxsequence=3, dictcheck=1</t>
+  </si>
+  <si>
+    <t>deny=5, unlock_time=1800</t>
+  </si>
+  <si>
+    <t>even_deny_root (có dòng này)</t>
+  </si>
+  <si>
+    <t>10. Sudo Hardening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  10.  Sudo Hardening</t>
+  </si>
+  <si>
+    <t>sudo grep 'use_pty' /etc/sudoers /etc/sudoers.d/ 2&gt;/dev/null</t>
+  </si>
+  <si>
+    <t>sudo grep -rP 'NOPASSWD' /etc/sudoers /etc/sudoers.d/ 2&gt;/dev/null | wc -l</t>
+  </si>
+  <si>
+    <t>sudo grep 'logfile' /etc/sudoers /etc/sudoers.d/ 2&gt;/dev/null</t>
+  </si>
+  <si>
+    <t>Defaults use_pty</t>
+  </si>
+  <si>
+    <t>0 (không có NOPASSWD)</t>
+  </si>
+  <si>
+    <t>Defaults logfile=/var/log/sudo.log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  11.  File Permissions</t>
+  </si>
+  <si>
+    <t>11. File Permissions</t>
+  </si>
+  <si>
+    <t>stat -c '%n %a %U:%G' /etc/shadow /etc/gshadow</t>
+  </si>
+  <si>
+    <t>stat -c '%n %a %U:%G' /etc/passwd /etc/group</t>
+  </si>
+  <si>
+    <t>stat -c '%n %a %U:%G' /etc/security/opasswd 2&gt;/dev/null</t>
+  </si>
+  <si>
+    <t>640 root:shadow</t>
+  </si>
+  <si>
+    <t>644 root:root</t>
+  </si>
+  <si>
+    <t>600 root:root</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1630,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1556,21 +1643,6 @@
         <color rgb="FFBFBFBF"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -1652,33 +1724,113 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1705,74 +1857,78 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2004,6 +2160,120 @@
           <bgColor rgb="FFE2EFDA"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF8C00"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2390,171 +2660,171 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
     </row>
     <row r="4" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
     </row>
     <row r="7" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="25"/>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="25"/>
+      <c r="D9" s="17"/>
     </row>
     <row r="10" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="25"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="25"/>
+      <c r="D11" s="17"/>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
       <c r="L15" s="2" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
     </row>
     <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
@@ -2564,11 +2834,11 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2591,16 +2861,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -3486,13 +3756,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="75.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -3501,1162 +3771,1596 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="33"/>
+      <c r="H2" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="12" t="s">
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" s="7">
+        <v>900</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+    </row>
+    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>22</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>23</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>24</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+    </row>
+    <row r="33" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>26</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>27</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>28</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>29</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>30</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+    </row>
+    <row r="39" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>31</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
         <v>32</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="12" t="s">
+      <c r="B40" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+    </row>
+    <row r="42" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
         <v>33</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="12" t="s">
+      <c r="B42" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
         <v>34</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="B43" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:9" s="29" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="B45" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
         <v>36</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="B46" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="B47" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="B48" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+    </row>
+    <row r="50" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="B50" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="B51" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="B52" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+    </row>
+    <row r="54" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
         <v>42</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="B54" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="B55" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+    </row>
+    <row r="57" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
         <v>44</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="B57" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>45</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="B58" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C58" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D58" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
+        <v>46</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+    </row>
+    <row r="61" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
         <v>47</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="B61" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="F61" s="7"/>
+      <c r="G61" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
         <v>48</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14" t="s">
+      <c r="B62" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C62" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
-        <v>2</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
+        <v>49</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+    </row>
+    <row r="65" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="40">
+        <f>COUNTA(G4:G63)</f>
         <v>45</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
-        <v>3</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="40"/>
+    </row>
+    <row r="66" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="40">
+        <f>COUNTIF(G4:G55,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+    </row>
+    <row r="67" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="40">
+        <f>COUNTIF(G4:G55,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40"/>
+    </row>
+    <row r="68" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="40">
+        <f>COUNTIF(G4:G63,"N/A")</f>
         <v>45</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
-        <v>4</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
-        <v>5</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="18">
-        <v>3</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>6</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <v>7</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-    </row>
-    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
-        <v>7</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <v>8</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
-        <v>9</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
-        <v>10</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-    </row>
-    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-    </row>
-    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
-        <v>11</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17">
-        <v>12</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-    </row>
-    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
-        <v>13</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
-        <v>14</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
-        <v>13</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-    </row>
-    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
-        <v>13</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
-        <v>14</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-    </row>
-    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
-        <v>15</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
-        <v>16</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-    </row>
-    <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-    </row>
-    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
-        <v>17</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
-        <v>18</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-    </row>
-    <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-    </row>
-    <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
-        <v>19</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-    </row>
-    <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17">
-        <v>20</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-    </row>
-    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-    </row>
-    <row r="35" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14">
-        <v>21</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-    </row>
-    <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="17">
-        <v>22</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-    </row>
-    <row r="37" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
-        <v>23</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-    </row>
-    <row r="38" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="17">
-        <v>24</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-    </row>
-    <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-    </row>
-    <row r="40" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="14">
-        <v>25</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-    </row>
-    <row r="41" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="17">
-        <v>26</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-    </row>
-    <row r="42" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="14">
-        <v>27</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="15"/>
-      <c r="G42" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-    </row>
-    <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="35"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-    </row>
-    <row r="44" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17">
-        <v>28</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-    </row>
-    <row r="45" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
-        <v>29</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-    </row>
-    <row r="47" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-    </row>
-    <row r="48" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="38">
-        <f>COUNTA(G4:G45)</f>
-        <v>32</v>
-      </c>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-    </row>
-    <row r="49" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="38">
-        <f>COUNTIF(G4:G45,"PASS")</f>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="40"/>
+      <c r="I68" s="40"/>
+    </row>
+    <row r="69" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="40">
+        <f>COUNTIFS(G4:G55,"FAIL",C4:C55,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-    </row>
-    <row r="50" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="38">
-        <f>COUNTIF(G4:G45,"FAIL")</f>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+    </row>
+    <row r="70" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="41">
+        <f>IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-    </row>
-    <row r="51" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="38">
-        <f>COUNTIF(G4:G45,"N/A")</f>
-        <v>32</v>
-      </c>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38"/>
-    </row>
-    <row r="52" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="38">
-        <f>COUNTIFS(G4:G45,"FAIL",C4:C45,"Cao")</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
-    </row>
-    <row r="53" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="39">
-        <f>IFERROR(COUNTIF(G4:G45,"PASS")/(COUNTA(G4:G45)-COUNTIF(G4:G45,"N/A")),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-    </row>
-    <row r="54" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="37" t="s">
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+    </row>
+    <row r="71" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="37"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="38" t="str">
-        <f>IF(IFERROR(COUNTIF(G4:G45,"PASS")/(COUNTA(G4:G45)-COUNTIF(G4:G45,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G45,"PASS")/(COUNTA(G4:G45)-COUNTIF(G4:G45,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="40" t="str">
+        <f>IF(IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-    </row>
-    <row r="56" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="37" t="s">
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+    </row>
+    <row r="73" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37" t="s">
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37" t="s">
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="I56" s="37"/>
+      <c r="I73" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="E53:I53"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:I54"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E50:I50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="E51:I51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:I48"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E49:I49"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A39:I39"/>
+  <mergeCells count="31">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:I67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:I70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E71:I71"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:I73"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G18 G22 G24:G45">
-    <cfRule type="cellIs" dxfId="38" priority="14" operator="equal">
+  <conditionalFormatting sqref="G32 G34:G55 G4:G28">
+    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="30" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="31" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E54:I54">
-    <cfRule type="cellIs" dxfId="35" priority="17" operator="equal">
+  <conditionalFormatting sqref="E71:I71">
+    <cfRule type="cellIs" dxfId="53" priority="32" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="33" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="34" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19:G21">
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+  <conditionalFormatting sqref="G29:G31">
+    <cfRule type="cellIs" dxfId="50" priority="19" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="20" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="21" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+  <conditionalFormatting sqref="G33">
+    <cfRule type="cellIs" dxfId="47" priority="16" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="17" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="18" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G56">
+    <cfRule type="cellIs" dxfId="41" priority="13" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="14" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G57:G59">
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="9" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G60">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G61:G63">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G1056" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G1073" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"PASS,FAIL,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4683,928 +5387,928 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="42">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="45">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="42">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="45">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="42">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
+      <c r="A10" s="45">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="42">
         <v>7</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
     </row>
     <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="45">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="42">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="45">
         <v>10</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="42">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+      <c r="A18" s="45">
         <v>12</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="42">
         <v>13</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
+      <c r="A21" s="45">
         <v>14</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
     </row>
     <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="42">
         <v>15</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="A23" s="45">
         <v>16</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
     </row>
     <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="42">
         <v>17</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
     </row>
     <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="45">
         <v>18</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
     </row>
     <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="42">
         <v>19</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="45">
         <v>20</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
     </row>
     <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="A29" s="42">
         <v>21</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
+      <c r="A30" s="45">
         <v>22</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="42">
         <v>23</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17">
+      <c r="A33" s="45">
         <v>24</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
     </row>
     <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="42">
         <v>25</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="17">
+      <c r="A36" s="45">
         <v>26</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
+      <c r="A37" s="42">
         <v>27</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="38">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="23">
         <f>COUNTA(G4:G37)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
     </row>
     <row r="41" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="37" t="s">
+      <c r="A41" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="38">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="23">
         <f>COUNTIF(G4:G37,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="37" t="s">
+      <c r="A42" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="38">
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="23">
         <f>COUNTIF(G4:G37,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
     </row>
     <row r="43" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="37" t="s">
+      <c r="A43" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="38">
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="23">
         <f>COUNTIF(G4:G37,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
     </row>
     <row r="44" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37" t="s">
+      <c r="A44" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38">
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="23">
         <f>COUNTIFS(G4:G37,"FAIL",C4:C37,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
     </row>
     <row r="45" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37" t="s">
+      <c r="A45" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="39">
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22">
         <f>IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
     </row>
     <row r="46" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="38" t="str">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="23" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
     </row>
     <row r="48" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37" t="s">
+      <c r="A48" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37" t="s">
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37" t="s">
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="37"/>
+      <c r="I48" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:I42"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:I45"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="H48:I48"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G37">
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46:I46">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F10">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5637,713 +6341,736 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="42">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="45">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="42">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
+      <c r="A9" s="45">
         <v>4</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
     </row>
     <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="42">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="45">
         <v>6</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
     </row>
     <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="42">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="45">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="42">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="45">
         <v>10</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="42">
         <v>11</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
     </row>
     <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="A20" s="45">
         <v>12</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="42">
         <v>13</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
     </row>
     <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="A23" s="45">
         <v>14</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="46" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="46" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
     </row>
     <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="42">
         <v>15</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="45">
         <v>16</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
     </row>
     <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="42">
         <v>17</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17">
+      <c r="A29" s="45">
         <v>18</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
     </row>
     <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="42">
         <v>19</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="43" t="s">
         <v>232</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="43" t="s">
         <v>233</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="41">
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="27">
         <f>COUNTA(G4:G30)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="41">
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="27">
         <f>COUNTIF(G4:G30,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="A35" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="41">
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="27">
         <f>COUNTIF(G4:G30,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="41">
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="27">
         <f>COUNTIF(G4:G30,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="41">
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="27">
         <f>COUNTIFS(G4:G30,"FAIL",C4:C30,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="42">
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26">
         <f>IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="41" t="str">
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="27" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34" t="s">
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="I41" s="34"/>
+      <c r="I41" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:I35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="A39:D39"/>
@@ -6351,47 +7078,26 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="H41:I41"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:I35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:I33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:I34"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G30">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:I39">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6424,713 +7130,736 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="42">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="45">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
     </row>
     <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="42">
         <v>3</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
+      <c r="A9" s="45">
         <v>4</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
     </row>
     <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="42">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="43" t="s">
         <v>240</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="45">
         <v>6</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="46" t="s">
         <v>241</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
     </row>
     <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="42">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="43" t="s">
         <v>242</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="45">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="46" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="42">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+      <c r="A17" s="45">
         <v>10</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="42">
         <v>11</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
     </row>
     <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="A20" s="45">
         <v>12</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
     </row>
     <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="42">
         <v>13</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="A23" s="45">
         <v>14</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
     </row>
     <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="42">
         <v>15</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="45">
         <v>16</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="46" t="s">
         <v>261</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="46" t="s">
         <v>233</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
     </row>
     <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="42">
         <v>17</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="43" t="s">
         <v>262</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="43" t="s">
         <v>233</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="45">
         <v>18</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="42">
         <v>19</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="43" t="s">
         <v>267</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="41">
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="27">
         <f>COUNTA(G4:G30)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="41">
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="27">
         <f>COUNTIF(G4:G30,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="A35" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="41">
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="27">
         <f>COUNTIF(G4:G30,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="41">
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="27">
         <f>COUNTIF(G4:G30,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="41">
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="27">
         <f>COUNTIFS(G4:G30,"FAIL",C4:C30,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="42">
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26">
         <f>IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="41" t="str">
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="27" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34" t="s">
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="I41" s="34"/>
+      <c r="I41" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:I35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="A39:D39"/>
@@ -7138,47 +7867,26 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="H41:I41"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:I35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:I33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:I34"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G30">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:I39">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7211,797 +7919,820 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="42">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="43" t="s">
         <v>272</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="45">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="42">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="45">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
     </row>
     <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="42">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+      <c r="A11" s="45">
         <v>6</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="42">
         <v>7</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+      <c r="A13" s="45">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="42">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="45">
         <v>10</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="42">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17">
+      <c r="A19" s="45">
         <v>12</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
     </row>
     <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="42">
         <v>13</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
     </row>
     <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17">
+      <c r="A22" s="45">
         <v>14</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
     </row>
     <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="42">
         <v>15</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="43" t="s">
         <v>294</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="43" t="s">
         <v>298</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
+      <c r="A24" s="45">
         <v>16</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
     </row>
     <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="42">
         <v>17</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="43" t="s">
         <v>304</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27" s="45">
         <v>18</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
     </row>
     <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="42">
         <v>19</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
+      <c r="A30" s="45">
         <v>20</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
     </row>
     <row r="31" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="A31" s="42">
         <v>21</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="43" t="s">
         <v>313</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
     </row>
     <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17">
+      <c r="A33" s="45">
         <v>22</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
     </row>
     <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="42">
         <v>23</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="43" t="s">
         <v>315</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="43" t="s">
         <v>318</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="41">
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="27">
         <f>COUNTA(G4:G34)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="41">
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="27">
         <f>COUNTIF(G4:G34,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="41">
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="27">
         <f>COUNTIF(G4:G34,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
     </row>
     <row r="40" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="41">
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="27">
         <f>COUNTIF(G4:G34,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="41">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="27">
         <f>COUNTIFS(G4:G34,"FAIL",C4:C34,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="42">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26">
         <f>IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
     </row>
     <row r="43" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="34" t="s">
+      <c r="A43" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="41" t="str">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="27" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="45" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34" t="s">
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34" t="s">
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="I45" s="34"/>
+      <c r="I45" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:I41"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="A43:D43"/>
@@ -8009,47 +8740,26 @@
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="H45:I45"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A14:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:I43">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/templates_excel/04_Đánh giá hệ thống hiện tại.xlsx
+++ b/templates_excel/04_Đánh giá hệ thống hiện tại.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/Hardening_System_Application/templates_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{E7230F2F-CFFB-45BF-80EB-743E8BFDA54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23E84EC-1B75-4031-B7F0-E17A98DF7DE8}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{E7230F2F-CFFB-45BF-80EB-743E8BFDA54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DEDE2AC-EC52-469A-BE49-BBC1749E91C7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng quan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="461">
   <si>
     <t>Mục đích:</t>
   </si>
@@ -195,18 +195,12 @@
     <t>grep MaxAuthTries /etc/ssh/sshd_config</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Trung bình</t>
   </si>
   <si>
     <t>grep LoginGraceTime /etc/ssh/sshd_config</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>grep X11Forwarding /etc/ssh/sshd_config</t>
   </si>
   <si>
@@ -1377,9 +1371,6 @@
     <t>difok=2, maxrepeat=3, maxsequence=3, dictcheck=1</t>
   </si>
   <si>
-    <t>deny=5, unlock_time=1800</t>
-  </si>
-  <si>
     <t>even_deny_root (có dòng này)</t>
   </si>
   <si>
@@ -1429,6 +1420,12 @@
   </si>
   <si>
     <t>600 root:root</t>
+  </si>
+  <si>
+    <t>10:30:60</t>
+  </si>
+  <si>
+    <t>deny=5, unlock_time=900</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1747,71 +1744,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1819,18 +1756,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1860,75 +1785,91 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
-    <dxf>
-      <font>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <font>
         <b/>
@@ -2259,21 +2200,35 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF595959"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FFFF8C00"/>
+        <color rgb="FFC00000"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FF00B050"/>
+        <color rgb="FF375623"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2660,171 +2615,171 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
     </row>
     <row r="4" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="7" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="28"/>
     </row>
     <row r="8" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="17"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="17"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="17"/>
+      <c r="D10" s="28"/>
     </row>
     <row r="11" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="17"/>
+      <c r="D11" s="28"/>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
     </row>
     <row r="13" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
       <c r="L15" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="B22" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
     </row>
     <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
@@ -2834,11 +2789,11 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2861,16 +2816,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -2903,13 +2858,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -2921,13 +2876,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -2939,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -2957,13 +2912,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -2975,13 +2930,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -2993,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -3011,13 +2966,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -3029,13 +2984,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -3047,13 +3002,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -3065,13 +3020,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -3083,13 +3038,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -3101,13 +3056,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -3119,13 +3074,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -3137,13 +3092,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -3155,13 +3110,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -3173,13 +3128,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -3191,13 +3146,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -3209,13 +3164,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -3227,13 +3182,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -3245,13 +3200,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -3263,13 +3218,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -3281,13 +3236,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3299,13 +3254,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>370</v>
-      </c>
       <c r="D25" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -3317,13 +3272,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -3335,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
@@ -3353,13 +3308,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>378</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>380</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
@@ -3371,13 +3326,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
@@ -3389,13 +3344,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
@@ -3407,13 +3362,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -3425,13 +3380,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>378</v>
-      </c>
       <c r="D32" s="11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
@@ -3443,13 +3398,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
@@ -3461,13 +3416,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
@@ -3479,13 +3434,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
@@ -3497,13 +3452,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
@@ -3515,13 +3470,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
@@ -3533,13 +3488,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
@@ -3551,13 +3506,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
@@ -3569,13 +3524,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -3587,13 +3542,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
@@ -3605,13 +3560,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
@@ -3623,13 +3578,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
@@ -3641,13 +3596,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
@@ -3659,13 +3614,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
@@ -3677,13 +3632,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
@@ -3695,13 +3650,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
@@ -3713,13 +3668,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
@@ -3731,13 +3686,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
@@ -3763,7 +3718,7 @@
     <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="64.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="75.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.21875" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
@@ -3771,36 +3726,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3817,7 +3772,7 @@
       <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="52" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -3834,17 +3789,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
@@ -3853,18 +3808,18 @@
       <c r="B5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="53" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -3876,18 +3831,18 @@
       <c r="B6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>50</v>
+      <c r="E6" s="53">
+        <v>4</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -3899,18 +3854,18 @@
       <c r="B7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>53</v>
+      <c r="E7" s="53">
+        <v>60</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -3922,18 +3877,18 @@
       <c r="B8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>51</v>
+      <c r="C8" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -3945,18 +3900,18 @@
       <c r="B9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="36" t="s">
-        <v>51</v>
+      <c r="C9" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="7">
+        <v>53</v>
+      </c>
+      <c r="E9" s="53">
         <v>3</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -3968,18 +3923,18 @@
       <c r="B10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>51</v>
+      <c r="C10" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="53" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -3991,18 +3946,18 @@
       <c r="B11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>422</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>54</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -4014,18 +3969,18 @@
       <c r="B12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="E12" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E12" s="53" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -4037,18 +3992,18 @@
       <c r="B13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>424</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -4060,18 +4015,18 @@
       <c r="B14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>51</v>
+      <c r="C14" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>66</v>
+        <v>432</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>64</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -4083,18 +4038,18 @@
       <c r="B15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>51</v>
+      <c r="C15" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E15" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="E15" s="53" t="s">
         <v>48</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -4106,18 +4061,18 @@
       <c r="B16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>51</v>
+      <c r="C16" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>439</v>
+        <v>434</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>437</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -4129,18 +4084,18 @@
       <c r="B17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.43819444444444444</v>
+        <v>435</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>459</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -4152,54 +4107,54 @@
       <c r="B18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="36" t="s">
-        <v>51</v>
+      <c r="C18" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="E18" s="7">
+        <v>436</v>
+      </c>
+      <c r="E18" s="53">
         <v>900</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
+      <c r="A19" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="53" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -4209,20 +4164,20 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>60</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4232,20 +4187,20 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>62</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4255,20 +4210,20 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>64</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4278,16 +4233,16 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>441</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="5"/>
@@ -4299,16 +4254,16 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>444</v>
+        <v>439</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>460</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="5"/>
@@ -4320,16 +4275,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>442</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>445</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="5"/>
@@ -4337,37 +4292,37 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
+      <c r="A27" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>22</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="53" t="s">
         <v>68</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -4377,20 +4332,20 @@
         <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>424</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4400,20 +4355,20 @@
         <v>24</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>70</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -4423,832 +4378,835 @@
         <v>25</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>426</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-    </row>
-    <row r="33" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+    </row>
+    <row r="33" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>26</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>430</v>
+        <v>427</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>428</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>27</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="53" t="s">
         <v>74</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="5"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>28</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>76</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>29</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>79</v>
+        <v>429</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>77</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>30</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>79</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-    </row>
-    <row r="39" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+    </row>
+    <row r="39" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>31</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="53" t="s">
         <v>83</v>
-      </c>
-      <c r="C39" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>32</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-    </row>
-    <row r="42" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+    </row>
+    <row r="42" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>33</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>51</v>
+        <v>87</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>422</v>
+        <v>88</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>420</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>34</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="D43" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="53" t="s">
         <v>91</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:9" s="29" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+    </row>
+    <row r="45" spans="1:9" s="12" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>35</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="53" t="s">
         <v>95</v>
-      </c>
-      <c r="C45" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>36</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>85</v>
+        <v>96</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>37</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>51</v>
+        <v>93</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>85</v>
+        <v>97</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>38</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>51</v>
+        <v>93</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>99</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-    </row>
-    <row r="50" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+    </row>
+    <row r="50" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>39</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="53" t="s">
         <v>103</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>40</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="53" t="s">
         <v>103</v>
-      </c>
-      <c r="C51" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>41</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E52" s="53" t="s">
         <v>103</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-    </row>
-    <row r="54" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+    </row>
+    <row r="54" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>42</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="53" t="s">
         <v>109</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>51</v>
+        <v>107</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>111</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="34" t="s">
-        <v>447</v>
-      </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34"/>
-      <c r="I56" s="34"/>
-    </row>
-    <row r="57" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="38" t="s">
+        <v>444</v>
+      </c>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+    </row>
+    <row r="57" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>44</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="C57" s="35" t="s">
+        <v>443</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E57" s="53" t="s">
         <v>448</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>451</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>45</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="C58" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D58" s="7" t="s">
+      <c r="E58" s="53" t="s">
         <v>449</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>452</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>46</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="C59" s="36" t="s">
-        <v>51</v>
+        <v>443</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E59" s="53" t="s">
         <v>450</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>453</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="34" t="s">
-        <v>454</v>
-      </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-    </row>
-    <row r="61" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+    </row>
+    <row r="61" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>47</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="C61" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D61" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E61" s="53" t="s">
         <v>456</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>459</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
     </row>
-    <row r="62" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>48</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="C62" s="36" t="s">
-        <v>51</v>
+        <v>452</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="D62" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E62" s="53" t="s">
         <v>457</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>460</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="1:9" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="12" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>49</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="C63" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D63" s="7" t="s">
+      <c r="E63" s="53" t="s">
         <v>458</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>461</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
+      <c r="A64" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
     </row>
     <row r="65" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="40">
+      <c r="A65" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="41">
         <f>COUNTA(G4:G63)</f>
         <v>45</v>
       </c>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="40"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
     </row>
     <row r="66" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B66" s="39"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="40">
+      <c r="A66" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="41">
         <f>COUNTIF(G4:G55,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="40"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
     </row>
     <row r="67" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="40">
+      <c r="A67" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="41">
         <f>COUNTIF(G4:G55,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="40"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41"/>
     </row>
     <row r="68" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="40">
+      <c r="A68" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="41">
         <f>COUNTIF(G4:G63,"N/A")</f>
         <v>45</v>
       </c>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="40"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41"/>
     </row>
     <row r="69" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="40">
+      <c r="A69" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="41">
         <f>COUNTIFS(G4:G55,"FAIL",C4:C55,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
     </row>
     <row r="70" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="41">
+      <c r="A70" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="42">
         <f>IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
     </row>
     <row r="71" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="B71" s="39"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="40" t="str">
+      <c r="A71" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="41" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G55,"PASS")/(COUNTA(G4:G55)-COUNTIF(G4:G55,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
     </row>
     <row r="73" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21" t="s">
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I73" s="21"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="I73" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:I70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E71:I71"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:I67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A64:I64"/>
     <mergeCell ref="A65:D65"/>
@@ -5257,72 +5215,69 @@
     <mergeCell ref="E66:I66"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="E67:I67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="E70:I70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="E71:I71"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A27:I27"/>
   </mergeCells>
   <conditionalFormatting sqref="G32 G34:G55 G4:G28">
-    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="29" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="30" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="31" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E71:I71">
-    <cfRule type="cellIs" dxfId="53" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="32" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="33" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="34" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:G31">
-    <cfRule type="cellIs" dxfId="50" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="21" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33">
-    <cfRule type="cellIs" dxfId="47" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="cellIs" dxfId="41" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="13" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="14" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5338,24 +5293,24 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G61:G63">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5366,7 +5321,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5387,36 +5342,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5450,865 +5405,865 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>1</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="E5" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>2</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D6" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45">
-        <v>2</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="47" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
+        <v>4</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="43" t="s">
+      <c r="D9" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-    </row>
-    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45">
-        <v>4</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="46" t="s">
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21">
+        <v>6</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-    </row>
-    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
-        <v>5</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="44" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45">
-        <v>6</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="47" t="s">
+      <c r="D12" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+    </row>
+    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>8</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-    </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42">
-        <v>7</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="44" t="s">
+      <c r="D14" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="43" t="s">
+      <c r="D15" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
+        <v>10</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-    </row>
-    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-    </row>
-    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
-        <v>8</v>
-      </c>
-      <c r="B14" s="46" t="s">
+      <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="F16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>11</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21">
+        <v>12</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-    </row>
-    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>9</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="44" t="s">
+      <c r="D18" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="22"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+    </row>
+    <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>13</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45">
-        <v>10</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="47" t="s">
+      <c r="D19" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+    </row>
+    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21">
+        <v>14</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-    </row>
-    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42">
-        <v>11</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-    </row>
-    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45">
-        <v>12</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="47" t="s">
+      <c r="D21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <v>15</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="F18" s="46"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-    </row>
-    <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42">
-        <v>13</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="44" t="s">
+      <c r="D22" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21">
+        <v>16</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
+        <v>17</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-    </row>
-    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-    </row>
-    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45">
-        <v>14</v>
-      </c>
-      <c r="B21" s="46" t="s">
+      <c r="D24" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
+        <v>18</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <v>19</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21">
+        <v>20</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" s="22"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+    </row>
+    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
+        <v>21</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="F29" s="19"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21">
+        <v>22</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+    </row>
+    <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+    </row>
+    <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <v>23</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-    </row>
-    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="42">
-        <v>15</v>
-      </c>
-      <c r="B22" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="44" t="s">
+      <c r="D32" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" s="19"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+    </row>
+    <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21">
+        <v>24</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="45">
-        <v>16</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-    </row>
-    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="42">
-        <v>17</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-    </row>
-    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-    </row>
-    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45">
-        <v>18</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-    </row>
-    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="42">
-        <v>19</v>
-      </c>
-      <c r="B27" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-    </row>
-    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45">
-        <v>20</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-    </row>
-    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="42">
-        <v>21</v>
-      </c>
-      <c r="B29" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="F29" s="43"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-    </row>
-    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45">
-        <v>22</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="E30" s="46" t="s">
+      <c r="D33" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <v>25</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-    </row>
-    <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-    </row>
-    <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="42">
-        <v>23</v>
-      </c>
-      <c r="B32" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="E32" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="F32" s="43"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-    </row>
-    <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45">
-        <v>24</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="46" t="s">
+      <c r="C34" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="46" t="s">
+      <c r="E34" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-    </row>
-    <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42">
-        <v>25</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="43" t="s">
+      <c r="F34" s="19"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+    </row>
+    <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+    </row>
+    <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21">
+        <v>26</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="F34" s="43"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-    </row>
-    <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="C36" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-    </row>
-    <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="45">
-        <v>26</v>
-      </c>
-      <c r="B36" s="46" t="s">
+      <c r="E36" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="46" t="s">
+      <c r="F36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+    </row>
+    <row r="37" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="18">
+        <v>27</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="46" t="s">
+      <c r="E37" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="F36" s="46"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-    </row>
-    <row r="37" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="42">
-        <v>27</v>
-      </c>
-      <c r="B37" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="F37" s="43"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="39" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
+      <c r="A39" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
     </row>
     <row r="40" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="23">
+      <c r="A40" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="45">
         <f>COUNTA(G4:G37)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
     </row>
     <row r="41" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="23">
+      <c r="A41" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="45">
         <f>COUNTIF(G4:G37,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="23">
+      <c r="A42" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="45">
         <f>COUNTIF(G4:G37,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
     </row>
     <row r="43" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="23">
+      <c r="A43" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="45">
         <f>COUNTIF(G4:G37,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
     </row>
     <row r="44" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="23">
+      <c r="A44" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="45">
         <f>COUNTIFS(G4:G37,"FAIL",C4:C37,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
     </row>
     <row r="45" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="22">
+      <c r="A45" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="46">
         <f>IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
     </row>
     <row r="46" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="23" t="str">
+      <c r="A46" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="45" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G37,"PASS")/(COUNTA(G4:G37)-COUNTIF(G4:G37,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
     </row>
     <row r="48" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21" t="s">
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I48" s="21"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="I48" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:I45"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="E42:I42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G37">
-    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46:I46">
-    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="9" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F10">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6341,36 +6296,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6404,673 +6359,652 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>1</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="E5" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>2</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D6" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E6" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45">
-        <v>2</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="47" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
+        <v>4</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="43" t="s">
+      <c r="D9" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-    </row>
-    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45">
-        <v>4</v>
-      </c>
-      <c r="B9" s="46" t="s">
+      <c r="C10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="E10" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21">
+        <v>6</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42">
-        <v>5</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="44" t="s">
+      <c r="D12" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="E10" s="43" t="s">
+      <c r="D13" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>8</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45">
-        <v>6</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="47" t="s">
+      <c r="C14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D14" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-    </row>
-    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42">
-        <v>7</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="44" t="s">
+      <c r="E14" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
+        <v>10</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
-        <v>8</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" s="47" t="s">
+      <c r="D16" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+    </row>
+    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>11</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>202</v>
-      </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-    </row>
-    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>9</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45">
-        <v>10</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="47" t="s">
+      <c r="D18" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21">
+        <v>12</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
+        <v>13</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21">
+        <v>14</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-    </row>
-    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-    </row>
-    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="42">
-        <v>11</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="44" t="s">
+      <c r="D23" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+    </row>
+    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18">
+        <v>15</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-    </row>
-    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-    </row>
-    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="45">
-        <v>12</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-    </row>
-    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42">
-        <v>13</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-    </row>
-    <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="45">
-        <v>14</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="C23" s="47" t="s">
+      <c r="D25" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
+        <v>16</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C26" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-    </row>
-    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-    </row>
-    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42">
-        <v>15</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="43" t="s">
+      <c r="D26" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E26" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="F25" s="43"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-    </row>
-    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45">
-        <v>16</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="46" t="s">
+      <c r="F26" s="22"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <v>17</v>
+      </c>
+      <c r="B28" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-    </row>
-    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
+      <c r="C28" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-    </row>
-    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="42">
-        <v>17</v>
-      </c>
-      <c r="B28" s="43" t="s">
+      <c r="E28" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="43" t="s">
+      <c r="F28" s="19"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21">
+        <v>18</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="E29" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-    </row>
-    <row r="29" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="45">
-        <v>18</v>
-      </c>
-      <c r="B29" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="46" t="s">
+      <c r="F29" s="22"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18">
+        <v>19</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="46" t="s">
+      <c r="E30" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-    </row>
-    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="42">
-        <v>19</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="A32" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
     </row>
     <row r="33" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="27">
+      <c r="A33" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="49">
         <f>COUNTA(G4:G30)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
     </row>
     <row r="34" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="27">
+      <c r="A34" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="49">
         <f>COUNTIF(G4:G30,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="27">
+      <c r="A35" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="49">
         <f>COUNTIF(G4:G30,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="27">
+      <c r="A36" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="49">
         <f>COUNTIF(G4:G30,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="27">
+      <c r="A37" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49">
         <f>COUNTIFS(G4:G30,"FAIL",C4:C30,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="26">
+      <c r="A38" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="50">
         <f>IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="27" t="str">
+      <c r="A39" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="49" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
     </row>
     <row r="41" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25" t="s">
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="25"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:I33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:I34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:I35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="A39:D39"/>
@@ -7078,26 +7012,47 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:I35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G30">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:I39">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7130,36 +7085,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7193,673 +7148,652 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="A4" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
+      <c r="A5" s="18">
         <v>1</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>2</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D6" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45">
-        <v>2</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="47" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+    </row>
+    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D8" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="F8" s="19"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
+        <v>4</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-    </row>
-    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
-        <v>3</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="44" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8" s="43" t="s">
+      <c r="D10" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-    </row>
-    <row r="9" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45">
-        <v>4</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="47" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21">
+        <v>6</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="E9" s="46" t="s">
+      <c r="D12" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42">
-        <v>5</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="44" t="s">
+      <c r="F12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="43" t="s">
+      <c r="D13" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45">
-        <v>6</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="47" t="s">
+      <c r="F13" s="19"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>8</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+    </row>
+    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21">
+        <v>10</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="22"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+    </row>
+    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>11</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21">
+        <v>12</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-    </row>
-    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42">
-        <v>7</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="44" t="s">
+      <c r="D20" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <v>13</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>242</v>
-      </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
-        <v>8</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-    </row>
-    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>9</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-    </row>
-    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="45">
-        <v>10</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-    </row>
-    <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="42">
-        <v>11</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-    </row>
-    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-    </row>
-    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="45">
-        <v>12</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="C20" s="47" t="s">
+      <c r="D22" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21">
+        <v>14</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>252</v>
-      </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-    </row>
-    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-    </row>
-    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="42">
-        <v>13</v>
-      </c>
-      <c r="B22" s="43" t="s">
+      <c r="D23" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="E23" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+    </row>
+    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18">
+        <v>15</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
+        <v>16</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <v>17</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21">
+        <v>18</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="F28" s="22"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18">
+        <v>19</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>255</v>
-      </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="45">
-        <v>14</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-    </row>
-    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="34" t="s">
-        <v>257</v>
-      </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-    </row>
-    <row r="25" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42">
-        <v>15</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>258</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>259</v>
-      </c>
-      <c r="E25" s="43" t="s">
-        <v>260</v>
-      </c>
-      <c r="F25" s="43"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-    </row>
-    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45">
-        <v>16</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-    </row>
-    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="42">
-        <v>17</v>
-      </c>
-      <c r="B27" s="43" t="s">
-        <v>258</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="E27" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-    </row>
-    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45">
-        <v>18</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="E28" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-    </row>
-    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
+      <c r="D30" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-    </row>
-    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="42">
-        <v>19</v>
-      </c>
-      <c r="B30" s="43" t="s">
+      <c r="E30" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>268</v>
-      </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="A32" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
     </row>
     <row r="33" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="27">
+      <c r="A33" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="49">
         <f>COUNTA(G4:G30)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
     </row>
     <row r="34" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="27">
+      <c r="A34" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="49">
         <f>COUNTIF(G4:G30,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="27">
+      <c r="A35" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="49">
         <f>COUNTIF(G4:G30,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="27">
+      <c r="A36" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="49">
         <f>COUNTIF(G4:G30,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="27">
+      <c r="A37" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49">
         <f>COUNTIFS(G4:G30,"FAIL",C4:C30,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="26">
+      <c r="A38" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="50">
         <f>IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="27" t="str">
+      <c r="A39" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="49" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G30,"PASS")/(COUNTA(G4:G30)-COUNTIF(G4:G30,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
     </row>
     <row r="41" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25" t="s">
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="25"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:I33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:I34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:I35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="A39:D39"/>
@@ -7867,26 +7801,47 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:I35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G30">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:I39">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7919,36 +7874,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7982,757 +7937,736 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>1</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="E5" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>2</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D6" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E6" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45">
-        <v>2</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="47" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D7" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E7" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="44" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
+        <v>4</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D10" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21">
+        <v>6</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21">
+        <v>8</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="E7" s="43" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-    </row>
-    <row r="8" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45">
-        <v>4</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>279</v>
-      </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-    </row>
-    <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42">
-        <v>5</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="44" t="s">
+      <c r="E13" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>281</v>
-      </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="45">
-        <v>6</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="47" t="s">
+      <c r="D15" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
+        <v>10</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-    </row>
-    <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42">
-        <v>7</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>283</v>
-      </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-    </row>
-    <row r="13" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45">
-        <v>8</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" s="47" t="s">
+      <c r="D16" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>11</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+    </row>
+    <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21">
+        <v>12</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+    </row>
+    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>13</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21">
+        <v>14</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>284</v>
-      </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-    </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-    </row>
-    <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>9</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>286</v>
-      </c>
-      <c r="C15" s="44" t="s">
+      <c r="D22" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F22" s="22"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="18">
+        <v>15</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>287</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45">
-        <v>10</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="47" t="s">
+      <c r="D23" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21">
+        <v>16</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-    </row>
-    <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42">
-        <v>11</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>289</v>
-      </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-    </row>
-    <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-    </row>
-    <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45">
-        <v>12</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>291</v>
-      </c>
-      <c r="F19" s="46"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-    </row>
-    <row r="20" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="42">
-        <v>13</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>292</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-    </row>
-    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-    </row>
-    <row r="22" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="45">
-        <v>14</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="47" t="s">
+      <c r="D24" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+    </row>
+    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <v>17</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="46" t="s">
-        <v>295</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="F22" s="46"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42">
-        <v>15</v>
-      </c>
-      <c r="B23" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="C23" s="44" t="s">
+      <c r="D26" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21">
+        <v>18</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="43" t="s">
-        <v>297</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>298</v>
-      </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-    </row>
-    <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="45">
-        <v>16</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>294</v>
-      </c>
-      <c r="C24" s="47" t="s">
+      <c r="D27" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="F27" s="22"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <v>19</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="F28" s="19"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21">
+        <v>20</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="C30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="46" t="s">
-        <v>299</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-    </row>
-    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-    </row>
-    <row r="26" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="42">
-        <v>17</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="C26" s="44" t="s">
+      <c r="D30" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+    </row>
+    <row r="31" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="18">
+        <v>21</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="43" t="s">
-        <v>303</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="F26" s="43"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-    </row>
-    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45">
-        <v>18</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="47" t="s">
+      <c r="D31" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+    </row>
+    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+    </row>
+    <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21">
+        <v>22</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="F27" s="46"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-    </row>
-    <row r="28" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="42">
-        <v>19</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>307</v>
-      </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-    </row>
-    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
-        <v>308</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-    </row>
-    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45">
-        <v>20</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="E30" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-    </row>
-    <row r="31" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="42">
-        <v>21</v>
-      </c>
-      <c r="B31" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>312</v>
-      </c>
-      <c r="E31" s="43" t="s">
+      <c r="D33" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <v>23</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="F31" s="43"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-    </row>
-    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="34" t="s">
-        <v>314</v>
-      </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-    </row>
-    <row r="33" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45">
-        <v>22</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>315</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="46" t="s">
+      <c r="C34" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="E33" s="46" t="s">
+      <c r="E34" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-    </row>
-    <row r="34" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42">
-        <v>23</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>318</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>319</v>
-      </c>
-      <c r="F34" s="43"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
+      <c r="A36" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="27">
+      <c r="A37" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49">
         <f>COUNTA(G4:G34)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="27">
+      <c r="A38" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="49">
         <f>COUNTIF(G4:G34,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
     </row>
     <row r="39" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="27">
+      <c r="A39" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="49">
         <f>COUNTIF(G4:G34,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
     </row>
     <row r="40" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="27">
+      <c r="A40" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="49">
         <f>COUNTIF(G4:G34,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
     </row>
     <row r="41" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="27">
+      <c r="A41" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="49">
         <f>COUNTIFS(G4:G34,"FAIL",C4:C34,"Cao")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="26">
+      <c r="A42" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="50">
         <f>IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="50"/>
     </row>
     <row r="43" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="27" t="str">
+      <c r="A43" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="49" t="str">
         <f>IF(IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)&gt;=0.9,"ĐẠT YÊU CẦU",IF(IFERROR(COUNTIF(G4:G34,"PASS")/(COUNTA(G4:G34)-COUNTIF(G4:G34,"N/A")),0)&gt;=0.8,"CẦN CẢI THIỆN (30 ngày)","KHÔNG ĐẠT – Khẩn cấp"))</f>
         <v>KHÔNG ĐẠT – Khẩn cấp</v>
       </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
     </row>
     <row r="45" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25" t="s">
+      <c r="B45" s="48"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="I45" s="25"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="I45" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:I41"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="A43:D43"/>
@@ -8740,26 +8674,47 @@
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="H45:I45"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A14:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:I43">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"CẦN CẢI THIỆN (30 ngày)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"KHÔNG ĐẠT – Khẩn cấp"</formula>
     </cfRule>
   </conditionalFormatting>
